--- a/nanshan_care_orders_fy_2025-05-01_2026-04-30.xlsx
+++ b/nanshan_care_orders_fy_2025-05-01_2026-04-30.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="年度养护" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="支付明细" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="支付流水" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="年度养护明细" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="年度养护" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="支付明细" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="支付流水" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="年度养护明细" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18234,7 +18234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H57"/>
+  <dimension ref="A1:I57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -18245,6 +18245,7 @@
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18288,6 +18289,11 @@
           <t>时间</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>操作人</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -18328,6 +18334,11 @@
           <t>14:34:40</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>张新健</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -18368,6 +18379,11 @@
           <t>14:36:49</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>陈晓庆</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -18408,6 +18424,11 @@
           <t>15:32:24</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>陈晓庆</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -18448,6 +18469,11 @@
           <t>17:12:11</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>张新健</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -18488,6 +18514,11 @@
           <t>11:52:24</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>张新健</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -18528,6 +18559,11 @@
           <t>21:59:41</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>张新健</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -18568,6 +18604,11 @@
           <t>22:02:06</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>张新健</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -18608,6 +18649,11 @@
           <t>13:06:31</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>汪树泉</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -18648,6 +18694,11 @@
           <t>12:04:57</t>
         </is>
       </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>汪树泉</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -18688,6 +18739,11 @@
           <t>18:09:46</t>
         </is>
       </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>汪树泉</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -18728,6 +18784,11 @@
           <t>10:29:30</t>
         </is>
       </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>舒武新（个人）</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -18758,6 +18819,11 @@
           <t>13:36:36</t>
         </is>
       </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>张新健</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -18788,6 +18854,11 @@
           <t>16:40:37</t>
         </is>
       </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>张新健</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -18828,6 +18899,11 @@
           <t>11:58:07</t>
         </is>
       </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>汪树泉</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -18868,6 +18944,11 @@
           <t>17:59:27</t>
         </is>
       </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>汪树泉</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -18908,6 +18989,11 @@
           <t>18:31:06</t>
         </is>
       </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>张新健</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -18948,6 +19034,11 @@
           <t>21:00:20</t>
         </is>
       </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>汪树泉</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -18988,6 +19079,11 @@
           <t>14:23:04</t>
         </is>
       </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>汪树泉</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -19028,6 +19124,11 @@
           <t>10:35:42</t>
         </is>
       </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>汪树泉</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -19068,6 +19169,11 @@
           <t>21:29:09</t>
         </is>
       </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>张新健</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -19108,6 +19214,11 @@
           <t>13:58:06</t>
         </is>
       </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>汪树泉</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -19148,6 +19259,11 @@
           <t>15:44:41</t>
         </is>
       </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>汪树泉</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -19188,6 +19304,11 @@
           <t>17:02:37</t>
         </is>
       </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>汪树泉</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -19228,6 +19349,11 @@
           <t>09:00:33</t>
         </is>
       </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>汪树泉</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -19268,6 +19394,11 @@
           <t>15:29:50</t>
         </is>
       </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>张新健</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -19308,6 +19439,11 @@
           <t>21:37:49</t>
         </is>
       </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>汪树泉</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -19348,6 +19484,11 @@
           <t>13:11:15</t>
         </is>
       </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>汪树泉</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -19388,6 +19529,11 @@
           <t>18:51:06</t>
         </is>
       </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>张新健</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -19423,6 +19569,11 @@
           <t>17:13:42</t>
         </is>
       </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>汪树泉</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -19463,6 +19614,11 @@
           <t>17:21:18</t>
         </is>
       </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>张新健</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -19503,6 +19659,11 @@
           <t>17:23:12</t>
         </is>
       </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>张新健</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -19543,6 +19704,11 @@
           <t>17:09:19</t>
         </is>
       </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>陈晓庆</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -19583,6 +19749,11 @@
           <t>18:35:52</t>
         </is>
       </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>陈晓庆</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -19618,6 +19789,11 @@
           <t>18:41:05</t>
         </is>
       </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>陈晓庆</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -19658,6 +19834,11 @@
           <t>17:07:37</t>
         </is>
       </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>汪树泉</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -19698,6 +19879,11 @@
           <t>15:06:36</t>
         </is>
       </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>张新健</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -19728,6 +19914,11 @@
           <t>19:55:44</t>
         </is>
       </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>张新健</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -19768,6 +19959,11 @@
           <t>16:29:45</t>
         </is>
       </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>汪树泉</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -19808,6 +20004,11 @@
           <t>14:49:27</t>
         </is>
       </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>汪树泉</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -19848,6 +20049,11 @@
           <t>20:35:44</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>汪树泉</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -19883,6 +20089,11 @@
           <t>16:24:14</t>
         </is>
       </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>汪树泉</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -19923,6 +20134,11 @@
           <t>11:43:14</t>
         </is>
       </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>汪树泉</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -19963,6 +20179,11 @@
           <t>18:27:05</t>
         </is>
       </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>张新健</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -20003,6 +20224,11 @@
           <t>09:40:41</t>
         </is>
       </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>汪树泉</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -20043,6 +20269,11 @@
           <t>16:51:13</t>
         </is>
       </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>汪树泉</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -20083,6 +20314,11 @@
           <t>13:36:29</t>
         </is>
       </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>汪树泉</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -20123,6 +20359,11 @@
           <t>13:38:01</t>
         </is>
       </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>汪树泉</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -20158,6 +20399,11 @@
           <t>12:21:35</t>
         </is>
       </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>张新健</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -20198,6 +20444,11 @@
           <t>13:49:39</t>
         </is>
       </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>汪树泉</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -20233,6 +20484,11 @@
           <t>17:09:11</t>
         </is>
       </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>汪树泉</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -20273,6 +20529,11 @@
           <t>13:27:37</t>
         </is>
       </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>汪树泉</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -20308,6 +20569,11 @@
           <t>10:14:13</t>
         </is>
       </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>汪树泉</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -20348,6 +20614,11 @@
           <t>10:10:28</t>
         </is>
       </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>张新健</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -20388,6 +20659,11 @@
           <t>21:57:23</t>
         </is>
       </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>汪树泉</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -20418,6 +20694,11 @@
           <t>12:30:02</t>
         </is>
       </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>张新健</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -20456,6 +20737,11 @@
       <c r="H57" t="inlineStr">
         <is>
           <t>15:42:53</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>张新健</t>
         </is>
       </c>
     </row>
